--- a/artfynd/A 34833-2023 artfynd.xlsx
+++ b/artfynd/A 34833-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34833-2023 artfynd.xlsx
+++ b/artfynd/A 34833-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>92140470</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -730,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>353048.4508864878</v>
+        <v>353048</v>
       </c>
       <c r="R2" t="n">
-        <v>6322399.575126059</v>
+        <v>6322400</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
